--- a/data/CV_masterfile.xlsx
+++ b/data/CV_masterfile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/helen_stoelting_monash_edu/Documents/Admin/CVs/Shiny_CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="659" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{221544F8-84D0-4222-A85E-299D0A54DF1E}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7FEA0E-C9DB-47F8-94ED-A737387FA531}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="2" activeTab="7" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Experience" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="382">
   <si>
     <t>Type</t>
   </si>
@@ -1185,6 +1185,30 @@
   </si>
   <si>
     <t>Department of Biochemistry and Molecular Biology;Infection Program;Biomedicine Discovery Institute;Monash University | 19 Innovation Walk;Clayton | VIC 3800 | Australia</t>
+  </si>
+  <si>
+    <t>09/2026</t>
+  </si>
+  <si>
+    <t>Visit to Helmholtz Munich</t>
+  </si>
+  <si>
+    <t>Munich, Germany</t>
+  </si>
+  <si>
+    <t>Helmholtz_Munich_Logo.jpg</t>
+  </si>
+  <si>
+    <t>EFIS ELINE.png</t>
+  </si>
+  <si>
+    <t>EFIS-ELINE Early-Life Immunity Satellite Workshop</t>
+  </si>
+  <si>
+    <t>55th Annual Meeting of the German Society for Immunology (DGfI)</t>
+  </si>
+  <si>
+    <t>DGfI.png</t>
   </si>
 </sst>
 </file>
@@ -1630,16 +1654,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0A4288-14F4-4FCB-B84F-D8D01C24F236}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="98.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="161.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="98.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="161.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1665,7 +1689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -1691,7 +1715,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -1717,7 +1741,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1743,7 +1767,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -1766,7 +1790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
@@ -1789,7 +1813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
@@ -1815,7 +1839,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
@@ -1838,7 +1862,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1864,7 +1888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
     </row>
   </sheetData>
@@ -1875,16 +1899,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA5BA22-B775-484F-B8E3-4AC9A669C82C}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="39.140625" customWidth="1"/>
+    <col min="2" max="3" width="23.7265625" customWidth="1"/>
+    <col min="6" max="6" width="39.1796875" customWidth="1"/>
     <col min="7" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1916,7 +1940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>56</v>
       </c>
@@ -1946,7 +1970,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>63</v>
       </c>
@@ -1978,7 +2002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>68</v>
       </c>
@@ -2018,14 +2042,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4AE233-F544-41E6-A9A2-E47CFF04CB58}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2069,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -2065,7 +2089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -2085,7 +2109,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -2105,7 +2129,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2125,7 +2149,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2145,7 +2169,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2172,17 +2196,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5E4C3E-ECD4-4E72-A578-49EE37F687E1}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.81640625" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>105</v>
       </c>
@@ -2202,262 +2226,256 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
         <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
         <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F10" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
         <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
         <v>115</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>127</v>
       </c>
-      <c r="F13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
       <c r="F14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>110</v>
       </c>
-      <c r="E15" t="s">
-        <v>127</v>
-      </c>
       <c r="F15" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
         <v>115</v>
@@ -2466,157 +2484,214 @@
         <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
         <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
         <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
         <v>127</v>
       </c>
       <c r="F18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
         <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>284</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
         <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>138</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
         <v>115</v>
       </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
       <c r="F23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B27" t="s">
         <v>291</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C27" t="s">
         <v>292</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D27" t="s">
         <v>142</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F27" t="s">
         <v>293</v>
       </c>
     </row>
@@ -2628,15 +2703,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C32E256-418F-4D73-88D3-033C6956F750}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>105</v>
       </c>
@@ -2656,7 +2731,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>211</v>
       </c>
@@ -2676,7 +2751,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>149</v>
       </c>
@@ -2690,7 +2765,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>151</v>
       </c>
@@ -2704,7 +2779,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>204</v>
       </c>
@@ -2721,7 +2796,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>154</v>
       </c>
@@ -2738,7 +2813,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>205</v>
       </c>
@@ -2758,7 +2833,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>58</v>
       </c>
@@ -2772,7 +2847,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>58</v>
       </c>
@@ -2786,7 +2861,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -2800,7 +2875,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>206</v>
       </c>
@@ -2817,7 +2892,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>157</v>
       </c>
@@ -2834,7 +2909,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>158</v>
       </c>
@@ -2848,7 +2923,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>160</v>
       </c>
@@ -2865,7 +2940,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>161</v>
       </c>
@@ -2882,7 +2957,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>161</v>
       </c>
@@ -2899,7 +2974,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>163</v>
       </c>
@@ -2913,7 +2988,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>33</v>
       </c>
@@ -2930,7 +3005,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>66</v>
       </c>
@@ -2947,7 +3022,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>37</v>
       </c>
@@ -2972,13 +3047,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B791D823-B9A3-4FB1-8BD6-3F1E7614E2A1}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="78.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>228</v>
       </c>
@@ -2989,7 +3064,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>301</v>
       </c>
@@ -3000,7 +3075,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>301</v>
       </c>
@@ -3011,7 +3086,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>301</v>
       </c>
@@ -3022,7 +3097,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>301</v>
       </c>
@@ -3033,7 +3108,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>301</v>
       </c>
@@ -3044,7 +3119,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>301</v>
       </c>
@@ -3055,7 +3130,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -3066,7 +3141,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>301</v>
       </c>
@@ -3077,7 +3152,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>301</v>
       </c>
@@ -3088,7 +3163,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>301</v>
       </c>
@@ -3099,7 +3174,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>302</v>
       </c>
@@ -3110,7 +3185,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>302</v>
       </c>
@@ -3121,7 +3196,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>302</v>
       </c>
@@ -3132,7 +3207,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -3143,7 +3218,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>236</v>
       </c>
@@ -3154,7 +3229,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -3165,7 +3240,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>236</v>
       </c>
@@ -3176,7 +3251,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>236</v>
       </c>
@@ -3187,7 +3262,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>236</v>
       </c>
@@ -3198,7 +3273,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>236</v>
       </c>
@@ -3209,7 +3284,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>236</v>
       </c>
@@ -3220,7 +3295,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>252</v>
       </c>
@@ -3231,7 +3306,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>252</v>
       </c>
@@ -3242,7 +3317,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>252</v>
       </c>
@@ -3253,7 +3328,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>252</v>
       </c>
@@ -3264,7 +3339,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>252</v>
       </c>
@@ -3275,7 +3350,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>240</v>
       </c>
@@ -3286,7 +3361,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>240</v>
       </c>
@@ -3297,7 +3372,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>240</v>
       </c>
@@ -3308,7 +3383,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>240</v>
       </c>
@@ -3319,7 +3394,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>240</v>
       </c>
@@ -3330,7 +3405,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>240</v>
       </c>
@@ -3341,7 +3416,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>240</v>
       </c>
@@ -3352,7 +3427,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>240</v>
       </c>
@@ -3363,7 +3438,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>240</v>
       </c>
@@ -3374,7 +3449,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>300</v>
       </c>
@@ -3385,7 +3460,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>300</v>
       </c>
@@ -3396,7 +3471,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>300</v>
       </c>
@@ -3407,7 +3482,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>300</v>
       </c>
@@ -3429,15 +3504,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F062-63AB-4258-BB2D-6AFC01AD9388}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="99" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="99" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3457,7 +3532,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>357</v>
       </c>
@@ -3471,7 +3546,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>357</v>
       </c>
@@ -3485,7 +3560,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>357</v>
       </c>
@@ -3499,7 +3574,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -3513,7 +3588,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>323</v>
       </c>
@@ -3527,7 +3602,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>324</v>
       </c>
@@ -3541,7 +3616,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>324</v>
       </c>
@@ -3555,7 +3630,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>324</v>
       </c>
@@ -3569,7 +3644,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>324</v>
       </c>
@@ -3583,7 +3658,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>324</v>
       </c>
@@ -3597,7 +3672,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>324</v>
       </c>
@@ -3611,7 +3686,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>308</v>
       </c>
@@ -3625,7 +3700,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>308</v>
       </c>
@@ -3639,7 +3714,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>308</v>
       </c>
@@ -3653,7 +3728,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>308</v>
       </c>
@@ -3667,7 +3742,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>308</v>
       </c>
@@ -3681,7 +3756,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>356</v>
       </c>
@@ -3700,12 +3775,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805B12EE-3B5F-4EF1-96D1-DE193CCF4A77}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3722,7 +3797,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>361</v>
       </c>
@@ -3739,7 +3814,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>364</v>
       </c>
@@ -3756,7 +3831,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>364</v>
       </c>

--- a/data/CV_masterfile.xlsx
+++ b/data/CV_masterfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/helen_stoelting_monash_edu/Documents/Admin/CVs/Shiny_CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7FEA0E-C9DB-47F8-94ED-A737387FA531}"/>
+  <xr:revisionPtr revIDLastSave="681" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E2915EF-D46A-4FFA-BAA7-34B69D84E341}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="383">
   <si>
     <t>Type</t>
   </si>
@@ -1209,6 +1209,9 @@
   </si>
   <si>
     <t>DGfI.png</t>
+  </si>
+  <si>
+    <t>Hosted by Dr Caspar Ohnmacht</t>
   </si>
 </sst>
 </file>
@@ -1334,6 +1337,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2273,6 +2280,9 @@
       <c r="D4" t="s">
         <v>112</v>
       </c>
+      <c r="E4" t="s">
+        <v>382</v>
+      </c>
       <c r="F4" t="s">
         <v>377</v>
       </c>

--- a/data/CV_masterfile.xlsx
+++ b/data/CV_masterfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/helen_stoelting_monash_edu/Documents/Admin/CVs/Shiny_CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="681" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E2915EF-D46A-4FFA-BAA7-34B69D84E341}"/>
+  <xr:revisionPtr revIDLastSave="690" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F2FC82-1544-4D96-85F9-25878D2DBDAB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="388">
   <si>
     <t>Type</t>
   </si>
@@ -1212,6 +1212,21 @@
   </si>
   <si>
     <t>Hosted by Dr Caspar Ohnmacht</t>
+  </si>
+  <si>
+    <t>Visit to Max Planck Institute of Biochemistry</t>
+  </si>
+  <si>
+    <t>Martinsried, Germany</t>
+  </si>
+  <si>
+    <t>Neuherberg, Germany</t>
+  </si>
+  <si>
+    <t>MPI.jpg</t>
+  </si>
+  <si>
+    <t>Hosted by Dr Patricia Ogger, Project Leader in the Immunoregulation group of Prof Peter Murray</t>
   </si>
 </sst>
 </file>
@@ -1337,10 +1352,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2203,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5E4C3E-ECD4-4E72-A578-49EE37F687E1}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -2238,16 +2249,19 @@
         <v>374</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>387</v>
       </c>
       <c r="F2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2255,16 +2269,16 @@
         <v>374</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C3" t="s">
         <v>376</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2272,87 +2286,87 @@
         <v>374</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C4" t="s">
         <v>376</v>
       </c>
       <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" t="s">
         <v>112</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>382</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>377</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2360,33 +2374,33 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
         <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2394,33 +2408,33 @@
         <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
         <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F11" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2428,36 +2442,33 @@
         <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
         <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
         <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2465,184 +2476,184 @@
         <v>155</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
         <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>115</v>
+      </c>
+      <c r="E15" t="s">
+        <v>127</v>
       </c>
       <c r="F15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
         <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
         <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
         <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
         <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="C22" t="s">
         <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
         <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
         <v>127</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -2651,38 +2662,41 @@
         <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
         <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="F26" t="s">
         <v>289</v>
@@ -2690,18 +2704,35 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>291</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>292</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>142</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>293</v>
       </c>
     </row>
